--- a/data/trans_camb/IP07_R2-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP07_R2-Provincia-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2,45</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>4,2</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3,74</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>-0,14</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>3,39</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>8,39</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2,45</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>4,2</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,4</t>
+          <t>3,12</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>5,83</t>
+          <t>3,44</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,74; 7,0</t>
+          <t>-2,4; 8,98</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,82; 12,19</t>
+          <t>-0,81; 11,69</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 31,63</t>
+          <t>-1,54; 10,18</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 8,82</t>
+          <t>-6,69; 6,95</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 11,06</t>
+          <t>-4,49; 11,91</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 9,92</t>
+          <t>-4,9; 11,04</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,97; 5,82</t>
+          <t>-3,18; 5,55</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 9,1</t>
+          <t>-0,71; 9,18</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,05; 16,69</t>
+          <t>-1,22; 8,47</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>105,11%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>180,28%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>160,37%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>-2,64%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>65,55%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>162,23%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>105,11%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>180,28%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>146,0%</t>
+          <t>60,29%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>159,01%</t>
+          <t>93,97%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-83,15; 474,98</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-56,83; 652,54</t>
+          <t>-69,64; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-47,78; 1781,66</t>
+          <t>-77,67; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-84,03; 400,83</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-73,72; —</t>
+          <t>-66,93; 692,54</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-75,93; —</t>
+          <t>-70,79; 632,21</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-59,9; 363,12</t>
+          <t>-63,63; 288,64</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-19,56; 559,17</t>
+          <t>-22,82; 468,72</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-20,9; 867,6</t>
+          <t>-32,98; 389,1</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0,04</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-0,75</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>-2,45</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>1,28</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>0,45</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>1,0</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,04</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-0,75</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-2,4</t>
+          <t>1,79</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-0,74</t>
+          <t>-0,43</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 4,95</t>
+          <t>-4,09; 4,05</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 3,93</t>
+          <t>-5,18; 3,32</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 4,69</t>
+          <t>-6,29; 0,9</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,91; 4,34</t>
+          <t>-1,82; 4,95</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,94; 3,68</t>
+          <t>-2,5; 3,94</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-6,1; 1,05</t>
+          <t>-1,51; 6,05</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 3,43</t>
+          <t>-2,13; 3,13</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 2,56</t>
+          <t>-2,76; 2,62</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-3,03; 1,73</t>
+          <t>-3,16; 2,12</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1,06%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-18,19%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>-59,16%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>70,88%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>24,87%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>55,27%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1,06%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-18,19%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-58,13%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-24,51%</t>
+          <t>-14,21%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-78,89; —</t>
+          <t>-69,01; 219,73</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-83,86; 174,88</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-84,96; 1064,0</t>
+          <t>-100,0; 97,51</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-67,5; 252,16</t>
+          <t>-85,61; 803,71</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-80,5; 211,76</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 107,47</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-46,61; 212,42</t>
+          <t>-52,46; 192,79</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-68,0; 138,64</t>
+          <t>-68,48; 171,57</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-73,54; 99,08</t>
+          <t>-73,46; 132,09</t>
         </is>
       </c>
     </row>
@@ -1056,34 +1056,34 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-1,72</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-2,64</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-0,32</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>-0,09</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-1,17</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>-1,17</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-1,72</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-2,64</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-0,36</t>
-        </is>
-      </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
           <t>-0,92</t>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-0,7</t>
+          <t>-0,73</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,53; 2,2</t>
+          <t>-5,27; 1,65</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,02; 0,0</t>
+          <t>-7,08; -0,87</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
+          <t>-4,09; 4,26</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>-3,61; 2,21</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>-5,83; 0,0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-5,27; 1,83</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-7,08; -0,86</t>
-        </is>
-      </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-4,2; 4,22</t>
+          <t>-5,88; 0,0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,55; 1,07</t>
+          <t>-3,32; 1,47</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-5,15; -0,57</t>
+          <t>-4,81; -0,45</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-3,16; 1,94</t>
+          <t>-3,37; 1,84</t>
         </is>
       </c>
     </row>
@@ -1162,47 +1162,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-65,19%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-11,98%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>-7,37%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-65,19%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>-47,91%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>-13,77%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>-47,91%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-36,53%</t>
+          <t>-38,03%</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-2,19</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-0,02</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-1,41</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>3,68</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>4,2</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>4,08</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-2,19</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-0,02</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-1,63</t>
+          <t>4,16</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1,12</t>
+          <t>1,32</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,08; 8,71</t>
+          <t>-6,77; 0,87</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,5; 9,45</t>
+          <t>-5,18; 4,81</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,12; 10,95</t>
+          <t>-5,45; 6,96</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-7,39; 0,82</t>
+          <t>1,04; 9,16</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-4,72; 4,5</t>
+          <t>1,5; 9,24</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-6,13; 4,53</t>
+          <t>1,15; 10,7</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 3,39</t>
+          <t>-2,14; 3,38</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 5,12</t>
+          <t>-0,81; 5,27</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 5,13</t>
+          <t>-1,62; 5,82</t>
         </is>
       </c>
     </row>
@@ -1378,34 +1378,34 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-62,46%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-0,69%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-40,39%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-62,46%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-0,69%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>-46,52%</t>
-        </is>
-      </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
           <t>37,43%</t>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>62,04%</t>
+          <t>73,18%</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-86,78; 388,34</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1461,17 +1461,17 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-74,3; 462,44</t>
+          <t>-75,0; 597,21</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-45,18; 758,33</t>
+          <t>-46,27; 816,56</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 903,66</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-0,62</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-7,76</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>-6,32</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>-4,69</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>-4,69</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-3,1</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-0,62</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-7,76</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-6,29</t>
+          <t>-3,23</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-4,75</t>
+          <t>-4,83</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-12,43; -1,48</t>
+          <t>-9,86; 7,27</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-12,68; -1,49</t>
+          <t>-15,65; -3,1</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-9,58; 1,77</t>
+          <t>-14,19; -0,32</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-9,73; 8,29</t>
+          <t>-12,58; -1,48</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-16,8; -3,02</t>
+          <t>-12,75; -1,49</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-15,47; -0,18</t>
+          <t>-10,86; 1,42</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-8,14; 2,09</t>
+          <t>-7,46; 2,44</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-11,58; -2,99</t>
+          <t>-11,97; -3,05</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-10,47; -0,88</t>
+          <t>-10,23; -0,72</t>
         </is>
       </c>
     </row>
@@ -1594,24 +1594,24 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-7,94%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>-81,41%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-66,19%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>-7,94%</t>
-        </is>
-      </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-80,99%</t>
+          <t>-68,88%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-75,7%</t>
+          <t>-76,9%</t>
         </is>
       </c>
     </row>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-81,37; 269,17</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1662,7 +1662,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-84,45; 269,97</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -1677,7 +1677,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-84,42; 87,47</t>
+          <t>-86,07; 93,23</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -1687,7 +1687,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 2,42</t>
+          <t>-100,0; 36,61</t>
         </is>
       </c>
     </row>
@@ -1704,32 +1704,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>-0,99</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>-0,73</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>0,88</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>0,15</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>0,01</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>0,31</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>-0,99</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>-0,73</t>
-        </is>
-      </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,84</t>
+          <t>0,25</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0,63</t>
+          <t>0,57</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-2,31; 3,97</t>
+          <t>-4,33; 3,37</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 3,52</t>
+          <t>-4,28; 3,59</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 4,47</t>
+          <t>-2,97; 6,69</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-4,39; 2,46</t>
+          <t>-2,31; 4,08</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-5,32; 3,09</t>
+          <t>-2,3; 3,61</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-4,33; 5,65</t>
+          <t>-2,3; 5,54</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-3,24; 1,99</t>
+          <t>-2,81; 2,15</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-2,79; 2,25</t>
+          <t>-2,79; 2,39</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 4,15</t>
+          <t>-2,27; 3,75</t>
         </is>
       </c>
     </row>
@@ -1810,32 +1810,32 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>-46,51%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>-34,1%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>41,27%</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>13,55%</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>0,65%</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>26,83%</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>-46,51%</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>-34,1%</t>
-        </is>
-      </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>39,35%</t>
+          <t>21,55%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>38,21%</t>
+          <t>34,76%</t>
         </is>
       </c>
     </row>
@@ -1903,7 +1903,7 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-89,38; —</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1920,32 +1920,32 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>-0,75</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>-0,63</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>1,32</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>0,39</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>-0,08</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>1,13</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>-0,75</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>-0,63</t>
-        </is>
-      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,17</t>
+          <t>1,22</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>1,22</t>
+          <t>1,31</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 2,42</t>
+          <t>-3,75; 1,69</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 1,82</t>
+          <t>-3,67; 1,93</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 4,29</t>
+          <t>-1,9; 4,8</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-3,97; 1,87</t>
+          <t>-1,67; 2,42</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-3,9; 1,86</t>
+          <t>-2,12; 1,48</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 4,91</t>
+          <t>-1,03; 4,7</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 1,51</t>
+          <t>-2,0; 1,73</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 1,31</t>
+          <t>-2,06; 1,21</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 3,67</t>
+          <t>-0,84; 3,7</t>
         </is>
       </c>
     </row>
@@ -2026,32 +2026,32 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>-29,98%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>-24,99%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>52,35%</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>37,49%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>-7,6%</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>108,68%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>-29,98%</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>-24,99%</t>
-        </is>
-      </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>46,45%</t>
+          <t>117,74%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>67,9%</t>
+          <t>73,04%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-89,31; 255,57</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-87,12; 316,78</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-57,21; 478,86</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 216,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-90,62; 199,16</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-65,11; 466,9</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-76,2; 182,18</t>
+          <t>-75,46; 211,49</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-78,34; 179,47</t>
+          <t>-77,53; 169,22</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-39,71; 431,91</t>
+          <t>-45,17; 370,24</t>
         </is>
       </c>
     </row>
@@ -2136,32 +2136,32 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>-2,54</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>-3,4</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>-3,56</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
           <t>1,08</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>-0,85</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>-0,85</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>-2,54</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>-3,4</t>
-        </is>
-      </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-3,57</t>
+          <t>-0,83</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-2,24</t>
+          <t>-2,22</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 4,29</t>
+          <t>-5,41; 0,3</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-2,85; 0,64</t>
+          <t>-6,33; -1,25</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-2,61; 1,21</t>
+          <t>-6,69; -1,16</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-5,84; 0,22</t>
+          <t>-1,12; 4,11</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-6,4; -1,19</t>
+          <t>-2,8; 0,72</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-6,51; -1,07</t>
+          <t>-2,7; 1,51</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-2,8; 1,27</t>
+          <t>-2,65; 1,18</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-3,94; -0,63</t>
+          <t>-3,86; -0,65</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-4,1; -0,69</t>
+          <t>-4,02; -0,64</t>
         </is>
       </c>
     </row>
@@ -2242,32 +2242,32 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>-61,28%</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>-81,93%</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>-85,81%</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
           <t>72,33%</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>-56,81%</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>-56,89%</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>-61,28%</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>-81,93%</t>
-        </is>
-      </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-86,08%</t>
+          <t>-55,43%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-78,64%</t>
+          <t>-78,05%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-66,18; 961,62</t>
+          <t>-88,55; 35,59</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; -12,94</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 11,33</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-91,65; 32,87</t>
+          <t>-55,37; 775,38</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -12,72</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 45,95</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-70,36; 82,1</t>
+          <t>-70,16; 81,08</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-94,18; -23,11</t>
+          <t>-94,86; -24,73</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -0,04</t>
+          <t>-100,0; -6,29</t>
         </is>
       </c>
     </row>
@@ -2352,32 +2352,32 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>-1,03</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>-1,44</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>-1,09</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
           <t>0,63</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>0,2</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>1,46</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>-1,03</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>-1,44</t>
-        </is>
-      </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>-1,08</t>
+          <t>0,85</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>0,14</t>
+          <t>-0,14</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 1,96</t>
+          <t>-2,51; 0,41</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 1,4</t>
+          <t>-2,99; -0,04</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-0,04; 5,02</t>
+          <t>-2,77; 0,47</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-2,44; 0,36</t>
+          <t>-0,6; 1,83</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-2,88; -0,09</t>
+          <t>-0,97; 1,34</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 0,36</t>
+          <t>-0,42; 2,38</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 0,76</t>
+          <t>-1,15; 0,68</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 0,23</t>
+          <t>-1,49; 0,25</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 1,85</t>
+          <t>-1,11; 0,85</t>
         </is>
       </c>
     </row>
@@ -2458,32 +2458,32 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>-29,26%</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>-40,83%</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>-30,76%</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
           <t>37,05%</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>11,97%</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>85,63%</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>-29,26%</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>-40,83%</t>
-        </is>
-      </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>-30,6%</t>
+          <t>49,91%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>-5,47%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-28,13; 159,34</t>
+          <t>-59,51; 14,7</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-41,7; 122,02</t>
+          <t>-65,92; 3,64</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-10,38; 335,25</t>
+          <t>-61,76; 19,4</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-56,8; 16,56</t>
+          <t>-28,29; 162,32</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-66,69; -0,86</t>
+          <t>-41,59; 117,53</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-59,93; 14,89</t>
+          <t>-19,61; 218,71</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-36,37; 35,79</t>
+          <t>-36,2; 31,75</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-49,59; 12,51</t>
+          <t>-48,15; 13,67</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-31,15; 75,32</t>
+          <t>-35,58; 39,58</t>
         </is>
       </c>
     </row>
